--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -34,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -48,15 +48,38 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,26 +497,26 @@
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>電子實習
-/ 邱聰輝教授</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
+邱聰輝教授</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>工智慧概論
-/ 賴文政教授</t>
+賴文政教授</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
           <t>英文聽講
-/ 吳柏德教授</t>
+吳柏德教授</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
           <t>工程數學
-/ 郭慶祥教授</t>
+郭慶祥教授</t>
         </is>
       </c>
     </row>
@@ -503,19 +526,19 @@
           <t>09:00~09:50</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="1" t="inlineStr"/>
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>工程數學
-/ 郭慶祥教授</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n"/>
+郭慶祥教授</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
           <t>人工智慧概論
-/ 賴文政教授</t>
+賴文政教授</t>
         </is>
       </c>
     </row>
@@ -525,11 +548,11 @@
           <t>10:00~10:50</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="1" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="1" t="inlineStr"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -537,11 +560,11 @@
           <t>11:00~11:50</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="1" t="inlineStr"/>
+      <c r="F5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,26 +572,11 @@
           <t>01:00~01:50</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>雲端化無限存取實務
-/ 劉恩成教授</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>自動控制與實習
-/ 謝飛虎教授</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>影像處理概論
-/ 王柏仁教授</t>
-        </is>
-      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -576,11 +584,11 @@
           <t>02:00~02:50</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n"/>
-      <c r="C7" s="1" t="n"/>
-      <c r="D7" s="1" t="n"/>
-      <c r="E7" s="1" t="n"/>
-      <c r="F7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -588,16 +596,11 @@
           <t>03:00~03:50</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>專題製作
-/ 祁存廣教授</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -605,22 +608,18 @@
           <t>04:00~04:50</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n"/>
-      <c r="C9" s="1" t="n"/>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-      <c r="F9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr"/>
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr"/>
+      <c r="F9" s="1" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E6:E9"/>
+  <mergeCells count="4">
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="D3:D5"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="課表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Timetable" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,38 +48,15 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,39 +434,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>週一</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>週二</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>週三</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>週四</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>週五</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>08:00~08:50</t>
         </is>
@@ -497,129 +474,153 @@
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>電子實習
-邱聰輝教授</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr"/>
+/ 邱聰輝教授</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>工智慧概論
-賴文政教授</t>
+          <t>人工智慧概論
+/ 賴文政教授</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
           <t>英文聽講
-吳柏德教授</t>
+/ 吳柏德教授</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
           <t>工程數學
-郭慶祥教授</t>
+/ 郭慶祥教授</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>09:00~09:50</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="1" t="inlineStr"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>工程數學
-郭慶祥教授</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n"/>
+/ 郭慶祥教授</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
           <t>人工智慧概論
-賴文政教授</t>
+/ 賴文政教授</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>10:00~10:50</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="1" t="inlineStr"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="1" t="inlineStr"/>
-      <c r="F4" s="3" t="n"/>
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>11:00~11:50</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="1" t="inlineStr"/>
-      <c r="F5" s="1" t="inlineStr"/>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>01:00~01:50</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
-      <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="1" t="inlineStr"/>
-      <c r="F6" s="1" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>13:00~13:50</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>雲端化無限存取實務
+/ 劉恩成教授</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>自動控制與實習
+/ 謝飛虎教授</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>影像處理概論
+/ 王柏仁教授</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>02:00~02:50</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>14:00~14:50</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>03:00~03:50</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr"/>
-      <c r="F8" s="1" t="inlineStr"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>15:00~15:50</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>專題製作
+/ 祁存廣教授</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>04:00~04:50</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr"/>
-      <c r="D9" s="1" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr"/>
-      <c r="F9" s="1" t="inlineStr"/>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>16:00~16:50</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="n"/>
+      <c r="D9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="D8:D9"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E6:E9"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
